--- a/house_sales_42731.xlsx
+++ b/house_sales_42731.xlsx
@@ -480,19 +480,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.01885</v>
+        <v>0.018513</v>
       </c>
       <c r="E2" t="n">
         <v>0.999858149</v>
       </c>
       <c r="F2" t="n">
-        <v>0.012576</v>
+        <v>0.012353</v>
       </c>
       <c r="G2" t="n">
         <v>0.855240645</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007587</v>
+        <v>0.007633</v>
       </c>
       <c r="I2" t="n">
         <v>3989925792</v>
@@ -515,19 +515,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.014012</v>
+        <v>0.013553</v>
       </c>
       <c r="E3" t="n">
         <v>0.99968094</v>
       </c>
       <c r="F3" t="n">
-        <v>0.007427</v>
+        <v>0.006755</v>
       </c>
       <c r="G3" t="n">
         <v>0.832171242</v>
       </c>
       <c r="H3" t="n">
-        <v>0.006272</v>
+        <v>0.005655</v>
       </c>
       <c r="I3" t="n">
         <v>3845312848</v>
@@ -550,19 +550,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.01774</v>
+        <v>0.018523</v>
       </c>
       <c r="E4" t="n">
         <v>0.999788571</v>
       </c>
       <c r="F4" t="n">
-        <v>0.012431</v>
+        <v>0.010539</v>
       </c>
       <c r="G4" t="n">
         <v>0.893202379</v>
       </c>
       <c r="H4" t="n">
-        <v>0.007171</v>
+        <v>0.007154</v>
       </c>
       <c r="I4" t="n">
         <v>4197924964</v>

--- a/house_sales_42731.xlsx
+++ b/house_sales_42731.xlsx
@@ -480,19 +480,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.018513</v>
+        <v>0.018803</v>
       </c>
       <c r="E2" t="n">
         <v>0.999858149</v>
       </c>
       <c r="F2" t="n">
-        <v>0.012353</v>
+        <v>0.014221</v>
       </c>
       <c r="G2" t="n">
         <v>0.855240645</v>
       </c>
       <c r="H2" t="n">
-        <v>0.007633</v>
+        <v>0.007528</v>
       </c>
       <c r="I2" t="n">
         <v>3989925792</v>
@@ -515,19 +515,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.013553</v>
+        <v>0.013458</v>
       </c>
       <c r="E3" t="n">
         <v>0.99968094</v>
       </c>
       <c r="F3" t="n">
-        <v>0.006755</v>
+        <v>0.007933000000000001</v>
       </c>
       <c r="G3" t="n">
         <v>0.832171242</v>
       </c>
       <c r="H3" t="n">
-        <v>0.005655</v>
+        <v>0.005609</v>
       </c>
       <c r="I3" t="n">
         <v>3845312848</v>
@@ -550,19 +550,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.018523</v>
+        <v>0.017692</v>
       </c>
       <c r="E4" t="n">
         <v>0.999788571</v>
       </c>
       <c r="F4" t="n">
-        <v>0.010539</v>
+        <v>0.011641</v>
       </c>
       <c r="G4" t="n">
         <v>0.893202379</v>
       </c>
       <c r="H4" t="n">
-        <v>0.007154</v>
+        <v>0.007269</v>
       </c>
       <c r="I4" t="n">
         <v>4197924964</v>
